--- a/artfynd/A 41651-2023 artfynd.xlsx
+++ b/artfynd/A 41651-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41651-2023 artfynd.xlsx
+++ b/artfynd/A 41651-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114716292</v>
+        <v>114716288</v>
       </c>
       <c r="B2" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>752009</v>
+        <v>751956</v>
       </c>
       <c r="R2" t="n">
-        <v>7430881</v>
+        <v>7430889</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,19 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114716288</v>
+        <v>114716289</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>751956</v>
+        <v>751882</v>
       </c>
       <c r="R3" t="n">
-        <v>7430889</v>
+        <v>7431012</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114716283</v>
+        <v>114716290</v>
       </c>
       <c r="B4" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>751874</v>
+        <v>751926</v>
       </c>
       <c r="R4" t="n">
-        <v>7430991</v>
+        <v>7430965</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114716282</v>
+        <v>114716291</v>
       </c>
       <c r="B5" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>751958</v>
+        <v>751951</v>
       </c>
       <c r="R5" t="n">
-        <v>7430900</v>
+        <v>7430927</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,19 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114716291</v>
+        <v>114716292</v>
       </c>
       <c r="B6" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>751951</v>
+        <v>752009</v>
       </c>
       <c r="R6" t="n">
-        <v>7430927</v>
+        <v>7430881</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,19 +1160,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114716289</v>
+        <v>114716293</v>
       </c>
       <c r="B7" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>751882</v>
+        <v>752013</v>
       </c>
       <c r="R7" t="n">
-        <v>7431012</v>
+        <v>7430880</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,19 +1257,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114716290</v>
+        <v>114716296</v>
       </c>
       <c r="B8" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>751926</v>
+        <v>752000</v>
       </c>
       <c r="R8" t="n">
-        <v>7430965</v>
+        <v>7430901</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1371,6 +1336,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1389,15 +1355,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114716293</v>
+        <v>114716282</v>
       </c>
       <c r="B9" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1366,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1390,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>752013</v>
+        <v>751958</v>
       </c>
       <c r="R9" t="n">
-        <v>7430880</v>
+        <v>7430900</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1488,6 +1449,103 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>114716283</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rantivaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>751874</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7430991</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-02-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-02-16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
